--- a/나보타_RAW.xlsx
+++ b/나보타_RAW.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\주민규\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\주민규\학소자료\7월\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>유형</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -95,6 +95,14 @@
   </si>
   <si>
     <t>매출액</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 재고금액(제품만)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고금액(제품만)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -555,6 +563,21 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -567,20 +590,8 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -864,15 +875,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:O9"/>
+  <dimension ref="B1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -916,8 +927,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="21" t="s">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -960,8 +971,8 @@
         <v>323.07888815174596</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="22"/>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="27"/>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1002,8 +1013,8 @@
         <v>107.43217356069319</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="22"/>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="27"/>
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
@@ -1044,140 +1055,240 @@
         <v>113.79290855294509</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="23"/>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="28"/>
       <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1">
+        <v>128.61807483999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>135.19160155</v>
+      </c>
+      <c r="F6" s="1">
+        <v>133.99155508000001</v>
+      </c>
+      <c r="G6" s="1">
+        <v>137.06295624000001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>121.59128661</v>
+      </c>
+      <c r="I6" s="16">
+        <v>100.10915599</v>
+      </c>
+      <c r="J6" s="17">
+        <f>J3/I3*I6</f>
+        <v>99.307375770810069</v>
+      </c>
+      <c r="K6" s="17">
+        <f t="shared" ref="K6:O6" si="0">K3/J3*J6</f>
+        <v>95.549749881174264</v>
+      </c>
+      <c r="L6" s="17">
+        <f t="shared" si="0"/>
+        <v>93.331955878364582</v>
+      </c>
+      <c r="M6" s="17">
+        <f t="shared" si="0"/>
+        <v>98.10055637688049</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="0"/>
+        <v>102.02190998839389</v>
+      </c>
+      <c r="O6" s="14">
+        <f t="shared" si="0"/>
+        <v>100.05209735126643</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="28"/>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1">
+        <v>37.260285000000003</v>
+      </c>
+      <c r="E7" s="1">
+        <v>35.173648450000002</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40.805624979999997</v>
+      </c>
+      <c r="G7" s="1">
+        <v>38.396520299999999</v>
+      </c>
+      <c r="H7" s="2">
+        <v>38.769296709999999</v>
+      </c>
+      <c r="I7" s="16">
+        <v>50.672093949999997</v>
+      </c>
+      <c r="J7" s="17">
+        <f>J6+J8-I6</f>
+        <v>41.681254976989891</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" ref="K7:O7" si="1">K6+K8-J6</f>
+        <v>48.387626704605196</v>
+      </c>
+      <c r="L7" s="17">
+        <f t="shared" si="1"/>
+        <v>57.71764213826431</v>
+      </c>
+      <c r="M7" s="17">
+        <f t="shared" si="1"/>
+        <v>38.595231121897072</v>
+      </c>
+      <c r="N7" s="17">
+        <f t="shared" si="1"/>
+        <v>45.103785538687902</v>
+      </c>
+      <c r="O7" s="14">
+        <f t="shared" si="1"/>
+        <v>48.34563661320631</v>
+      </c>
+      <c r="Q7" s="30"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="28"/>
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D8" s="1">
         <v>43.369109190000003</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E8" s="1">
         <v>28.600121739999999</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F8" s="1">
         <v>42.005671450000001</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G8" s="1">
         <v>35.325119139999998</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H8" s="2">
         <v>54.24096634</v>
       </c>
-      <c r="I6" s="16">
-        <v>49.962649059347292</v>
-      </c>
-      <c r="J6" s="17">
+      <c r="I8" s="16">
+        <v>72.154224569999997</v>
+      </c>
+      <c r="J8" s="17">
         <v>42.483035196179813</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K8" s="17">
         <v>52.145252594241015</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L8" s="17">
         <v>59.935436141074</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M8" s="17">
         <v>33.826630623381178</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N8" s="17">
         <v>41.182431927174498</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O8" s="14">
         <v>50.315449250333778</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="24"/>
-      <c r="C7" s="6" t="s">
+    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="29"/>
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D9" s="3">
         <v>81.909740303205496</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E9" s="3">
         <v>138.92069525567376</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F9" s="3">
         <v>106.67094630141192</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G9" s="3">
         <v>104.05217942401599</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H9" s="4">
         <v>86.683560105861901</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I9" s="18">
         <v>83.694146654403781</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J9" s="3">
         <v>85.549382988396914</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K9" s="3">
         <v>87.588705931189523</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L9" s="3">
         <v>78.649026444719723</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M9" s="3">
         <v>104.24449852536409</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N9" s="3">
         <v>94.923401008386193</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O9" s="4">
         <v>85.175489121475039</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="25"/>
-      <c r="C8" s="26" t="s">
+    <row r="10" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27">
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23">
         <v>226</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G10" s="23">
         <v>19</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H10" s="24">
         <v>402</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I10" s="25">
         <v>428</v>
       </c>
-      <c r="J8" s="27">
-        <f>$I$8/$I$6*J6</f>
-        <v>363.92664132694199</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" ref="K8:O8" si="0">$I$8/$I$6*K6</f>
-        <v>446.69705330926092</v>
-      </c>
-      <c r="L8" s="27">
-        <f t="shared" si="0"/>
-        <v>513.43087589108688</v>
-      </c>
-      <c r="M8" s="27">
-        <f t="shared" si="0"/>
-        <v>289.77242358806745</v>
-      </c>
-      <c r="N8" s="27">
-        <f t="shared" si="0"/>
-        <v>352.78515444394952</v>
-      </c>
-      <c r="O8" s="28">
-        <f t="shared" si="0"/>
-        <v>431.02222729549135</v>
+      <c r="J10" s="23">
+        <f>$I$10/$I$8*J8</f>
+        <v>251.99826028654888</v>
+      </c>
+      <c r="K10" s="23">
+        <f>$I$10/$I$8*K8</f>
+        <v>309.31200831745224</v>
+      </c>
+      <c r="L10" s="23">
+        <f>$I$10/$I$8*L8</f>
+        <v>355.52134086748003</v>
+      </c>
+      <c r="M10" s="23">
+        <f>$I$10/$I$8*M8</f>
+        <v>200.65073102908332</v>
+      </c>
+      <c r="N10" s="23">
+        <f>$I$10/$I$8*N8</f>
+        <v>244.2834216551083</v>
+      </c>
+      <c r="O10" s="24">
+        <f>$I$10/$I$8*O8</f>
+        <v>298.45809316751496</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="H9" s="20"/>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M12" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B3:B9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
